--- a/forms/trg/Formulir_TRG_shrimpfarming.xlsx
+++ b/forms/trg/Formulir_TRG_shrimpfarming.xlsx
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>COUNTA(Anggota!B5:B26)</f>
+        <f>COUNTA(Anggota!B5:B27)</f>
         <v/>
       </c>
     </row>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!F5:F26)</f>
+        <f>COUNTA(Anggota!F5:F27)</f>
         <v/>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M26"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -913,39 +913,23 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Dr. Ir. Badraeni, MP</t>
+          <t>Prof. Ir. Muhammad Iqbal Djawad, M.Sc, Ph.D.</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>Hasanuddin University</t>
-        </is>
-      </c>
-      <c r="E5" s="11" t="inlineStr">
-        <is>
-          <t>Water Quality of Aquaculture</t>
-        </is>
-      </c>
+          <t>Leader</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="n"/>
+      <c r="E5" s="11" t="n"/>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="12" t="n"/>
       <c r="H5" s="12" t="n"/>
       <c r="I5" s="12" t="n"/>
       <c r="J5" s="12" t="n"/>
-      <c r="K5" s="11" t="inlineStr">
-        <is>
-          <t>6005391</t>
-        </is>
-      </c>
-      <c r="L5" s="11" t="inlineStr">
-        <is>
-          <t>57192374833</t>
-        </is>
-      </c>
+      <c r="K5" s="12" t="n"/>
+      <c r="L5" s="12" t="n"/>
       <c r="M5" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -958,12 +942,12 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Dr. Ir. Dody Dharmawan, M.App.Sc</t>
+          <t>Dr. Ir. Badraeni, MP</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
@@ -973,7 +957,7 @@
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>Hatchery Management of Shrimp</t>
+          <t>Water Quality of Aquaculture</t>
         </is>
       </c>
       <c r="F6" s="12" t="n"/>
@@ -983,12 +967,12 @@
       <c r="J6" s="12" t="n"/>
       <c r="K6" s="11" t="inlineStr">
         <is>
-          <t>6010427</t>
+          <t>6005391</t>
         </is>
       </c>
       <c r="L6" s="11" t="inlineStr">
         <is>
-          <t>6504470095</t>
+          <t>57192374833</t>
         </is>
       </c>
       <c r="M6" s="11" t="inlineStr">
@@ -1003,12 +987,12 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Ir. Zainuddin, M.Si</t>
+          <t>Dr. Ir. Dody Dharmawan, M.App.Sc</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
@@ -1018,7 +1002,7 @@
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>Nutritional Biochemistry</t>
+          <t>Hatchery Management of Shrimp</t>
         </is>
       </c>
       <c r="F7" s="12" t="n"/>
@@ -1028,12 +1012,12 @@
       <c r="J7" s="12" t="n"/>
       <c r="K7" s="11" t="inlineStr">
         <is>
-          <t>5979366</t>
+          <t>6010427</t>
         </is>
       </c>
       <c r="L7" s="11" t="inlineStr">
         <is>
-          <t>58220583400</t>
+          <t>6504470095</t>
         </is>
       </c>
       <c r="M7" s="11" t="inlineStr">
@@ -1048,12 +1032,12 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Dr. Ir. Badraeni, MP</t>
+          <t>Prof. Dr. Ir. Zainuddin, M.Si</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
@@ -1063,7 +1047,7 @@
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>Water Quality of Aquaculture</t>
+          <t>Nutritional Biochemistry</t>
         </is>
       </c>
       <c r="F8" s="12" t="n"/>
@@ -1073,12 +1057,12 @@
       <c r="J8" s="12" t="n"/>
       <c r="K8" s="11" t="inlineStr">
         <is>
-          <t>6005391</t>
+          <t>5979366</t>
         </is>
       </c>
       <c r="L8" s="11" t="inlineStr">
         <is>
-          <t>57192374833</t>
+          <t>58220583400</t>
         </is>
       </c>
       <c r="M8" s="11" t="inlineStr">
@@ -1093,12 +1077,12 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Dr. Ir. Dody Dharmawan, M.App.Sc</t>
+          <t>Dr. Ir. Badraeni, MP</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
@@ -1108,7 +1092,7 @@
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>Hatchery Management of Shrimp</t>
+          <t>Water Quality of Aquaculture</t>
         </is>
       </c>
       <c r="F9" s="12" t="n"/>
@@ -1118,12 +1102,12 @@
       <c r="J9" s="12" t="n"/>
       <c r="K9" s="11" t="inlineStr">
         <is>
-          <t>6010427</t>
+          <t>6005391</t>
         </is>
       </c>
       <c r="L9" s="11" t="inlineStr">
         <is>
-          <t>6504470095</t>
+          <t>57192374833</t>
         </is>
       </c>
       <c r="M9" s="11" t="inlineStr">
@@ -1138,12 +1122,12 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Ir. Zainuddin, M.Si</t>
+          <t>Dr. Ir. Dody Dharmawan, M.App.Sc</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
@@ -1153,7 +1137,7 @@
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>Nutritional Biochemistry</t>
+          <t>Hatchery Management of Shrimp</t>
         </is>
       </c>
       <c r="F10" s="12" t="n"/>
@@ -1163,12 +1147,12 @@
       <c r="J10" s="12" t="n"/>
       <c r="K10" s="11" t="inlineStr">
         <is>
-          <t>5979366</t>
+          <t>6010427</t>
         </is>
       </c>
       <c r="L10" s="11" t="inlineStr">
         <is>
-          <t>58220583400</t>
+          <t>6504470095</t>
         </is>
       </c>
       <c r="M10" s="11" t="inlineStr">
@@ -1183,22 +1167,22 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Ahmad Fikri Abdullah</t>
+          <t>Prof. Dr. Ir. Zainuddin, M.Si</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>Universiti Putra Malaysia</t>
+          <t>Hasanuddin University</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>Water Science Engineering</t>
+          <t>Nutritional Biochemistry</t>
         </is>
       </c>
       <c r="F11" s="12" t="n"/>
@@ -1206,10 +1190,14 @@
       <c r="H11" s="12" t="n"/>
       <c r="I11" s="12" t="n"/>
       <c r="J11" s="12" t="n"/>
-      <c r="K11" s="12" t="n"/>
+      <c r="K11" s="11" t="inlineStr">
+        <is>
+          <t>5979366</t>
+        </is>
+      </c>
       <c r="L11" s="11" t="inlineStr">
         <is>
-          <t>55142706500</t>
+          <t>58220583400</t>
         </is>
       </c>
       <c r="M11" s="11" t="inlineStr">
@@ -1224,22 +1212,22 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Anugerah Saputra, S.Pi. M.Si</t>
+          <t>Prof. Dr. Ahmad Fikri Abdullah</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>Hasanuddin University</t>
+          <t>Universiti Putra Malaysia</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>Aquaculture</t>
+          <t>Water Science Engineering</t>
         </is>
       </c>
       <c r="F12" s="12" t="n"/>
@@ -1248,7 +1236,11 @@
       <c r="I12" s="12" t="n"/>
       <c r="J12" s="12" t="n"/>
       <c r="K12" s="12" t="n"/>
-      <c r="L12" s="12" t="n"/>
+      <c r="L12" s="11" t="inlineStr">
+        <is>
+          <t>55142706500</t>
+        </is>
+      </c>
       <c r="M12" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1261,12 +1253,12 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Sitti Faridah</t>
+          <t>Anugerah Saputra, S.Pi. M.Si</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
@@ -1276,7 +1268,7 @@
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>Feed Nutritional</t>
+          <t>Aquaculture</t>
         </is>
       </c>
       <c r="F13" s="12" t="n"/>
@@ -1298,12 +1290,12 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Amirah Izzah Amany</t>
+          <t>Sitti Faridah</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
@@ -1313,7 +1305,7 @@
       </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
-          <t>Fisiology of fish respon</t>
+          <t>Feed Nutritional</t>
         </is>
       </c>
       <c r="F14" s="12" t="n"/>
@@ -1333,10 +1325,26 @@
       <c r="A15" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="12" t="n"/>
-      <c r="C15" s="12" t="n"/>
-      <c r="D15" s="12" t="n"/>
-      <c r="E15" s="11" t="n"/>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>Amirah Izzah Amany</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>Hasanuddin University</t>
+        </is>
+      </c>
+      <c r="E15" s="11" t="inlineStr">
+        <is>
+          <t>Fisiology of fish respon</t>
+        </is>
+      </c>
       <c r="F15" s="12" t="n"/>
       <c r="G15" s="12" t="n"/>
       <c r="H15" s="12" t="n"/>
@@ -1344,7 +1352,11 @@
       <c r="J15" s="12" t="n"/>
       <c r="K15" s="12" t="n"/>
       <c r="L15" s="12" t="n"/>
-      <c r="M15" s="12" t="n"/>
+      <c r="M15" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
@@ -1533,15 +1545,32 @@
       <c r="L26" s="12" t="n"/>
       <c r="M26" s="12" t="n"/>
     </row>
+    <row r="27">
+      <c r="A27" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="12" t="n"/>
+      <c r="C27" s="12" t="n"/>
+      <c r="D27" s="12" t="n"/>
+      <c r="E27" s="11" t="n"/>
+      <c r="F27" s="12" t="n"/>
+      <c r="G27" s="12" t="n"/>
+      <c r="H27" s="12" t="n"/>
+      <c r="I27" s="12" t="n"/>
+      <c r="J27" s="12" t="n"/>
+      <c r="K27" s="12" t="n"/>
+      <c r="L27" s="12" t="n"/>
+      <c r="M27" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
